--- a/data/sales_data.xlsx
+++ b/data/sales_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A492BFF5-C4C4-4FD5-AA37-124E65C556D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE19006A-2EAE-49A3-A027-CBE096150B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B0D279A9-84FC-4459-A808-5C40DF9616A0}"/>
   </bookViews>
